--- a/03_Prompting/outputs/GPT/RESULT_f-droid_gpt-4o_zeroshot_cot.xlsx
+++ b/03_Prompting/outputs/GPT/RESULT_f-droid_gpt-4o_zeroshot_cot.xlsx
@@ -782,7 +782,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -9573,7 +9573,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -10848,7 +10848,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -11103,7 +11103,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -11154,7 +11154,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -11851,7 +11851,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -12463,7 +12463,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -12531,7 +12531,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -12837,7 +12837,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -13279,7 +13279,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -13364,7 +13364,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -14129,7 +14129,7 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -14469,7 +14469,7 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15183,7 +15183,7 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15268,7 +15268,7 @@
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15353,7 +15353,7 @@
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15693,7 +15693,7 @@
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15999,7 +15999,7 @@
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -16101,7 +16101,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -16288,7 +16288,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -16526,7 +16526,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -17155,7 +17155,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -17631,7 +17631,7 @@
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -17648,7 +17648,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -17767,7 +17767,7 @@
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18039,7 +18039,7 @@
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18209,7 +18209,7 @@
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -18328,7 +18328,7 @@
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18583,7 +18583,7 @@
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18651,7 +18651,7 @@
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -19263,7 +19263,7 @@
       </c>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -19739,7 +19739,7 @@
       </c>
       <c r="C1136" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -19756,7 +19756,7 @@
       </c>
       <c r="C1137" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -20045,7 +20045,7 @@
       </c>
       <c r="C1154" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -20266,7 +20266,7 @@
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -20419,7 +20419,7 @@
       </c>
       <c r="C1176" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -20487,7 +20487,7 @@
       </c>
       <c r="C1180" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -20521,7 +20521,7 @@
       </c>
       <c r="C1182" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -20589,7 +20589,7 @@
       </c>
       <c r="C1186" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -20742,7 +20742,7 @@
       </c>
       <c r="C1195" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -22255,7 +22255,7 @@
       </c>
       <c r="C1284" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -25884,7 +25884,7 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -26615,7 +26615,7 @@
       </c>
       <c r="C1540" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="C1561" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="C1750" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="C1934" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -38481,7 +38481,7 @@
       </c>
       <c r="C2238" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -43020,7 +43020,7 @@
       </c>
       <c r="C2505" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -43700,7 +43700,7 @@
       </c>
       <c r="C2545" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -48443,7 +48443,7 @@
       </c>
       <c r="C2824" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -48786,7 +48786,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6494192185850053</v>
+        <v>0.6360436466033087</v>
       </c>
     </row>
     <row r="3">
@@ -48796,7 +48796,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5405384867190423</v>
+        <v>0.5109155168762463</v>
       </c>
     </row>
     <row r="4">
@@ -48806,7 +48806,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5749425936065519</v>
+        <v>0.5489677038565707</v>
       </c>
     </row>
     <row r="5">
@@ -48816,7 +48816,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7633575616537718</v>
+        <v>0.7652341683581014</v>
       </c>
     </row>
     <row r="6">
@@ -48826,7 +48826,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5884632486632509</v>
+        <v>0.5717689857965015</v>
       </c>
     </row>
     <row r="7">
@@ -48836,7 +48836,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>805.2016431169995</v>
+        <v>1595.210885213979</v>
       </c>
     </row>
     <row r="8">
@@ -48846,7 +48846,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2834219088760998</v>
+        <v>0.5614962637148817</v>
       </c>
     </row>
   </sheetData>
